--- a/ig/ch-term/ValueSet-ch-vacd-swissmedic-vaccines-vs.xlsx
+++ b/ig/ch-term/ValueSet-ch-vacd-swissmedic-vaccines-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="297">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -576,6 +576,12 @@
     <t>ProQuad</t>
   </si>
   <si>
+    <t>65728</t>
+  </si>
+  <si>
+    <t>Gardasil 9 (Durchstechflasche)</t>
+  </si>
+  <si>
     <t>65387</t>
   </si>
   <si>
@@ -669,7 +675,7 @@
     <t>68358</t>
   </si>
   <si>
-    <t>Ervebo, Injektionslösung</t>
+    <t>Ervebo</t>
   </si>
   <si>
     <t>68710-01</t>
@@ -723,13 +729,13 @@
     <t>69123</t>
   </si>
   <si>
-    <t>Spikevax Bivalent Original / Omicron 10 mg/ml, Fertigspritze</t>
+    <t>Spikevax Bivalent Original / Omicron 10 mg/ml</t>
   </si>
   <si>
     <t>69010</t>
   </si>
   <si>
-    <t>Spikevax, Fertigspritze</t>
+    <t>Spikevax</t>
   </si>
   <si>
     <t>69047</t>
@@ -753,9 +759,6 @@
     <t>69211</t>
   </si>
   <si>
-    <t>Spikevax Bivalent Original / Omicron BA.4-5, Fertigspritze</t>
-  </si>
-  <si>
     <t>68752</t>
   </si>
   <si>
@@ -810,31 +813,31 @@
     <t>69913</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 0.042 mg, Injektionsdispersion in einer Fertigspritze, Pfizer AG</t>
+    <t>Comirnaty JN.1 0.042 mg</t>
   </si>
   <si>
     <t>69912-01</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 30 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 30 µg</t>
   </si>
   <si>
     <t>69912-02</t>
   </si>
   <si>
-    <t>Comirnaty JN.1 10 μg, Injektionsdispersion, Pfizer AG</t>
+    <t>Comirnaty JN.1 10 µg</t>
   </si>
   <si>
     <t>69691</t>
   </si>
   <si>
-    <t>Abrysvo, Pulver und Lösungsmittel zur Herstellung einer Injektionslösung, Pfizer AG</t>
+    <t>Abrysvo</t>
   </si>
   <si>
     <t>69788</t>
   </si>
   <si>
-    <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml, Dispersion zur Injektion, Moderna Switzerland GmbH</t>
+    <t>Spikevax JN.1 (mRNA-1273.167), 0.10mg/ml</t>
   </si>
   <si>
     <t>70205</t>
@@ -846,43 +849,52 @@
     <t>70400</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 10 μg</t>
+    <t>Comirnaty LP.8.1 10 µg</t>
   </si>
   <si>
     <t>70403</t>
   </si>
   <si>
-    <t>Comirnaty LP.8.1 30 μg</t>
+    <t>Comirnaty LP.8.1 30 µg</t>
   </si>
   <si>
     <t>69863-01</t>
   </si>
   <si>
-    <t>Efluelda TIV 0.5 mL, suspension injectable en seringue pré-remplie	Sanofi-Aventis (Suisse) SA</t>
+    <t>Efluelda TIV 0.5 mL</t>
   </si>
   <si>
     <t>69995-01</t>
   </si>
   <si>
-    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml, Injektionsdispersion	Moderna Switzerland GmbH</t>
+    <t>mResvia Respiratorisches-Synzytial-Virus (RSV) Vakzin 0.10 mg/ml</t>
   </si>
   <si>
     <t>69781</t>
   </si>
   <si>
-    <t>Capvaxive, Injektionslösung in Fertigspritze MSD Merck Sharp &amp; Dohme AG</t>
+    <t>Capvaxive</t>
   </si>
   <si>
     <t>70042</t>
   </si>
   <si>
-    <t>Fluarix, Injektionssuspension GlaxoSmithKline AG</t>
-  </si>
-  <si>
     <t>69992</t>
   </si>
   <si>
-    <t>Influvac 0.5 ml, Injektionssuspension in einer Fertigspritze Viatris Pharma GmbH</t>
+    <t>Influvac 0.5 ml</t>
+  </si>
+  <si>
+    <t>70144</t>
+  </si>
+  <si>
+    <t>Flucelvax</t>
+  </si>
+  <si>
+    <t>70490</t>
+  </si>
+  <si>
+    <t>Vimkunya</t>
   </si>
   <si>
     <t/>
@@ -1165,7 +1177,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B133"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -2049,23 +2061,23 @@
         <v>247</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>250</v>
       </c>
     </row>
     <row r="113">
@@ -2073,167 +2085,191 @@
         <v>252</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>255</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>257</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="B116" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>259</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="B117" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>261</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="B118" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>263</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="B119" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>265</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="B120" t="s" s="2">
         <v>266</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>267</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="B121" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>269</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="B122" t="s" s="2">
         <v>270</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>271</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="B123" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="B124" t="s" s="2">
         <v>274</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>275</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="B125" t="s" s="2">
         <v>276</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>277</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="B126" t="s" s="2">
         <v>278</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>279</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="B127" t="s" s="2">
         <v>280</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>281</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="B128" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B129" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>285</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B130" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>287</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>289</v>
+        <v>74</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B133" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="B133" t="s" s="2">
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
         <v>292</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="B135" t="s" s="2">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="B136" t="s" s="2">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
